--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0230.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0230.xlsx
@@ -7204,7 +7204,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>???</t>
+          <t>Cái gì cơ???</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Số lượng Cộng Hưởng Giả trong đội hình thử thách Tháp Nghịch Cảnh đã vượt quá giới hạn. Hãy thử lại</t>
+          <t>Số lượng Resonator trong đội hình thử thách Tháp Nghịch Cảnh đã vượt quá giới hạn. Hãy thử lại</t>
         </is>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Không thể có Cộng Hưởng Giả trùng lặp trong đội hình thử thách Tháp Nghịch Cảnh. Hãy thử lại.</t>
+          <t>Không thể có Resonator trùng lặp trong đội hình thử thách Tháp Nghịch Cảnh. Hãy thử lại.</t>
         </is>
       </c>
     </row>
@@ -13639,7 +13639,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Chức năng này không tồn tại trong Công cụ, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức.</t>
+          <t>Chức năng này không tồn tại trong Utility, nếu có thắc mắc, vui lòng liên hệ bộ phận chăm sóc khách hàng chính thức.</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Tải Thiết Lập Hiện Tại: &lt;color=#a4e058&gt;Smooth&lt;/color&gt;</t>
+          <t>Tải Thiết Lập Hiện Tại: &lt;color=#a4e058&gt;Mượt&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Tải Thiết Lập Hiện Tại: &lt;color=#f6b065&gt;Laggy&lt;/color&gt;</t>
+          <t>Tải Thiết Lập Hiện Tại: &lt;color=#f6b065&gt;Giật Lag&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Tải Thiết Lập Hiện Tại: &lt;color=#f66d6d&gt;Overloaded&lt;/color&gt;</t>
+          <t>Tải Thiết Lập Hiện Tại: &lt;color=#f66d6d&gt;Quá Tải&lt;/color&gt;</t>
         </is>
       </c>
     </row>
@@ -27224,7 +27224,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Exploration Progress: {0}</t>
+          <t>Tiến Độ Thám Hiểm: {0}</t>
         </is>
       </c>
     </row>
@@ -32229,7 +32229,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Điều chỉnh Ghi chú thất bại, vui lòng thử lại.</t>
+          <t>Điều chỉnh Note thất bại, vui lòng thử lại.</t>
         </is>
       </c>
     </row>
